--- a/data/trans_orig/IP07C06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C06-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>22826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>30288</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35732</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>28330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59058</t>
+          <t>58092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65259</t>
+          <t>65505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>81076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76585</t>
+          <t>76061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92933</t>
+          <t>93052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146768</t>
+          <t>146819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169765</t>
+          <t>169385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -1449,47 +1449,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5986</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>38778</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>39821</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>50600</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72547</t>
+          <t>72071</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43766</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20990</t>
+          <t>20617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36183</t>
+          <t>36364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74118</t>
+          <t>74687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99680</t>
+          <t>98683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120070</t>
+          <t>120621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112992</t>
+          <t>113096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133642</t>
+          <t>133251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217588</t>
+          <t>218436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>247895</t>
+          <t>248229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29049</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46385</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37058</t>
+          <t>36234</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56567</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70051</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>97288</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51439</t>
+          <t>51222</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73525</t>
+          <t>72891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38200</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59619</t>
+          <t>58512</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94911</t>
+          <t>95847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>125630</t>
+          <t>126408</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170047</t>
+          <t>170079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>196278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195584</t>
+          <t>196076</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>221918</t>
+          <t>221481</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371172</t>
+          <t>370811</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>408075</t>
+          <t>408622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27067</t>
+          <t>25959</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45920</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46732</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34649</t>
+          <t>34517</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53358</t>
+          <t>52853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76598</t>
+          <t>76889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78212</t>
+          <t>79214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>97661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>86220</t>
+          <t>86641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106322</t>
+          <t>105435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170792</t>
+          <t>169748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199464</t>
+          <t>197611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6153</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38201</t>
+          <t>38556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27400</t>
+          <t>26700</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44030</t>
+          <t>44223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53683</t>
+          <t>52807</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76406</t>
+          <t>76378</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44298</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>27114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58291</t>
+          <t>58905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82373</t>
+          <t>82136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74276</t>
+          <t>75191</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96234</t>
+          <t>96488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82715</t>
+          <t>82564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103406</t>
+          <t>104645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161864</t>
+          <t>163857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193719</t>
+          <t>193036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55820</t>
+          <t>56263</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65195</t>
+          <t>65796</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>85494</t>
+          <t>84654</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116026</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61425</t>
+          <t>61969</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85615</t>
+          <t>86353</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73248</t>
+          <t>73308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117099</t>
+          <t>117436</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150878</t>
+          <t>151131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159391</t>
+          <t>158722</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188221</t>
+          <t>187007</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174505</t>
+          <t>173440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203625</t>
+          <t>203531</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342251</t>
+          <t>342725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384527</t>
+          <t>383667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15443</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30996</t>
+          <t>30553</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30800</t>
+          <t>30158</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>35051</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58230</t>
+          <t>56913</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33147</t>
+          <t>34283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>44442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49401</t>
+          <t>49656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72826</t>
+          <t>74677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107541</t>
+          <t>106527</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127436</t>
+          <t>127744</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96994</t>
+          <t>96438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118383</t>
+          <t>118447</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209032</t>
+          <t>210709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>240421</t>
+          <t>240852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23559</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14711</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29968</t>
+          <t>30138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50086</t>
+          <t>49613</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32678</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51663</t>
+          <t>51463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43324</t>
+          <t>44707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65473</t>
+          <t>63821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80437</t>
+          <t>81268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109536</t>
+          <t>108903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72823</t>
+          <t>72232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93613</t>
+          <t>93724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73817</t>
+          <t>75441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96500</t>
+          <t>97844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153782</t>
+          <t>154171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184229</t>
+          <t>184865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>34161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54815</t>
+          <t>55873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51946</t>
+          <t>52980</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54888</t>
+          <t>54533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>70702</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>99276</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>55379</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80223</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>76168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104155</t>
+          <t>102962</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139592</t>
+          <t>137332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176228</t>
+          <t>174457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184767</t>
+          <t>186369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214667</t>
+          <t>216364</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177055</t>
+          <t>176833</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>210486</t>
+          <t>207611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>374696</t>
+          <t>370732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>415294</t>
+          <t>415043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C06-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el/la menor [KIDSCREEN 20] en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3543</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1270</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3900</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4395</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3177</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4237</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2062</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5535</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5810</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>1,85%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4240</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15699</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10128</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22029</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3275</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11895</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3667</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12134</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15699</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10512</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22826</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>15945</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30288</t>
+          <t>29836</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20338</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14889</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28157</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>27665</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20584</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>35383</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>21663</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>38239</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>24,88%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20338</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14377</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>28330</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58092</t>
+          <t>57829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84844</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>76797</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92464</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>62,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>73513</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>65505</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>81076</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>64783</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>81046</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,12%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>84844</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>76061</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>93052</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>69,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146819</t>
+          <t>146857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169385</t>
+          <t>168887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122908</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122908</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122908</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111184</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111184</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111184</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122908</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>122908</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>122908</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,92 +1404,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5401</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5315</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3173</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4092</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8334</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3695</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30835</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23035</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39239</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>21,24%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>30092</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22900</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38778</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>21980</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>38719</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16,82%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>30835</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23718</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39821</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>50600</t>
+          <t>49599</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72071</t>
+          <t>71559</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27847</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20532</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36728</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>34589</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>25736</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>43739</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>26368</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>43112</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>27847</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>20617</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>36364</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50615</t>
+          <t>51027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74687</t>
+          <t>73923</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>123336</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>114000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>133489</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>110162</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>98683</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>120621</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>99578</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>120473</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>123336</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>113096</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>133251</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,78%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218436</t>
+          <t>218491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>248229</t>
+          <t>248310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184703</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184703</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184703</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184703</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184703</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184703</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2638</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6004</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1270</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4515</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4464</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2638</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6613</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5521</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>6154</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10655</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2862</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10868</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5537</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46533</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>37155</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56880</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>18,49%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>36765</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>29049</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>46843</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>27766</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>46099</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>12,67%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46533</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>36234</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>56972</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70261</t>
+          <t>70063</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>97185</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>48185</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>38043</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>59158</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12,37%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>62254</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>51222</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>72891</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>51699</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>74774</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>21,46%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>48185</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>39144</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>58512</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95847</t>
+          <t>97931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126408</t>
+          <t>127313</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>208180</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>196430</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>222067</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>63,86%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>72,19%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>183676</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>170079</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>196278</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>170149</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>196421</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>63,31%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>58,62%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>67,65%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>208180</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>196076</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>221481</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>67,68%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>370811</t>
+          <t>374423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>408622</t>
+          <t>410777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>307611</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>307611</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>307611</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>290119</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>290119</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>290119</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>307611</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>307611</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>307611</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el/la menor [KIDSCREEN 20] en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2941</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6857</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7515</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6030</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2769</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11832</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7038</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3786</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12126</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4664</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9585</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8904</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>3,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7038</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3621</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12197</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19040</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13003</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26450</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15900</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10195</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22816</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10798</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>23230</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,6%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19040</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13066</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26571</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25959</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>45650</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26450</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18667</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34019</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>38071</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30421</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47980</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>29419</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>47129</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,39%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26450</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19406</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34517</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52853</t>
+          <t>52735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76889</t>
+          <t>76825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96125</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>85954</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>106215</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>62,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>55,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>88388</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>79214</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>97661</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>78534</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>98350</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>58,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96125</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>86641</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>105435</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169748</t>
+          <t>170064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197611</t>
+          <t>198817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,26%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154683</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154683</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154683</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154683</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154683</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154683</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6137</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4825</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8899</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2159</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9624</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2464</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5607</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3793,107 +3793,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4643</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9188</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>7078</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3543</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12950</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3745</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12657</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>4,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4643</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9511</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>11721</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>7218</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>18594</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>5,6%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>11721</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>7065</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>18763</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>34910</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27554</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43884</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>20,54%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>25,82%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29680</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>21841</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38556</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>21544</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>38083</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>18,3%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>23,77%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>34910</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>26700</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>44223</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52807</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76378</t>
+          <t>77765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34880</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26675</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44328</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>35188</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27568</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>44217</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>27451</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>44960</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>21,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>34880</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>27114</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>44441</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58905</t>
+          <t>57974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82136</t>
+          <t>83165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>93032</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>81514</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>102829</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>85437</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>75191</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96488</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>74554</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>95443</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>52,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>93032</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>82564</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>104645</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>54,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163857</t>
+          <t>162404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193036</t>
+          <t>192477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169929</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169929</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169929</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>169929</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>169929</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>169929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8494</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4560</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14023</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>7767</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4162</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13330</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13385</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8494</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14623</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>23968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11681</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17914</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>11743</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7472</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18177</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>18499</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>3,76%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>11681</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>7212</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>19692</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>53950</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>42528</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>64480</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19,86%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>45580</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>36435</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>56263</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>36281</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>57076</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>14,6%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>53950</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>43111</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>65796</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84654</t>
+          <t>84727</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114939</t>
+          <t>114659</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>61330</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>51115</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>73828</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,89%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>73259</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>61969</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>86353</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>61631</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>86439</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>23,47%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>61330</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>50027</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>73308</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117436</t>
+          <t>118502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151131</t>
+          <t>152074</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>189157</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>173840</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>202671</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>58,27%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>53,55%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>62,43%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>173825</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>158722</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>187007</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>159064</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>188629</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>55,68%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>50,84%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>59,9%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>189157</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>173440</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>203531</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>58,27%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342725</t>
+          <t>343150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>383667</t>
+          <t>382471</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>324612</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>324612</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>324612</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>312174</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>324612</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>324612</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>324612</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el/la menor [KIDSCREEN 20] en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2671</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4665</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9332</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8747</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2671</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6726</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9175</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4783</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9545</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5481</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15234</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5664</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15508</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>5,31%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9175</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4873</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15833</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12360</t>
+          <t>12638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26644</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -5505,67 +5505,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>22834</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16442</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>31059</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,83%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>22659</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15739</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30553</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>30909</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,61%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22834</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>15655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>30158</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35051</t>
+          <t>35075</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56913</t>
+          <t>56404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35272</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27515</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45464</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>25194</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18010</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34283</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17817</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33186</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>35272</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>27456</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>44442</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49656</t>
+          <t>48474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74677</t>
+          <t>72447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108033</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>97440</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>118746</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>66,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>117631</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>106527</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>127744</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>107473</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>128332</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,46%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108033</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>96438</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>118447</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>60,7%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210709</t>
+          <t>210290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>240852</t>
+          <t>240379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,21%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>177985</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>177985</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>177985</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>179694</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>179694</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>179694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>177985</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>177985</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>177985</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2981</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7610</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4455</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1842</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8510</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8857</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2981</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>817</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7166</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8157</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3957</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13516</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16592</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10926</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24001</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10996</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>23784</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>10,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8157</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4405</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14192</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33866</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -6187,67 +6187,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>20187</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28672</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>18739</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12506</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26441</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12264</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26255</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>11,37%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>20187</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13724</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28163</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30138</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49613</t>
+          <t>50093</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53563</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43613</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64209</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>41677</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32931</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51463</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32727</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>51062</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>53563</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44707</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>63821</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81268</t>
+          <t>81626</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108903</t>
+          <t>109891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>85704</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>73669</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>96583</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>50,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>83343</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72232</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>93724</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>73152</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>93827</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>50,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>85704</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75441</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>97844</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>50,24%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154171</t>
+          <t>152349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184865</t>
+          <t>183596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5652</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10730</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9121</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5108</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15756</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5307</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15116</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5652</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2737</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10380</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21955</t>
+          <t>22071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17332</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11661</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24577</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>26137</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19021</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>35233</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>18488</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>34992</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>7,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>17332</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>11325</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>25063</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34161</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55873</t>
+          <t>54526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -6869,67 +6869,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>43020</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>34112</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>54652</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9,79%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>15,68%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>41398</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>32009</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>52980</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>31974</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>52458</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>12,02%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>43020</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33783</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>54533</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70702</t>
+          <t>70611</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>98423</t>
+          <t>98834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>88835</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>75321</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>103794</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>25,49%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>21,61%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>66871</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>55379</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>80531</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>54680</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>79759</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>19,41%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>16,08%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>88835</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>76168</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>102962</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>25,49%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137332</t>
+          <t>137163</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174457</t>
+          <t>174463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7090,74 +7090,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>193737</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>176879</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>208667</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>55,58%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>50,74%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>59,86%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>200974</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>186369</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>216364</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>184478</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>216397</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>58,34%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>54,1%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>53,55%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>62,81%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>193737</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>176833</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>207611</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>55,58%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>50,73%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>59,56%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>548</t>
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>370732</t>
+          <t>371317</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>415043</t>
+          <t>416506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>348577</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>348577</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>348577</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>491</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>344501</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>344501</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>344501</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>348577</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>348577</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>348577</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
